--- a/artfynd/A 32502-2026 artfynd.xlsx
+++ b/artfynd/A 32502-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69300329</v>
+        <v>136293882</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531232</v>
+        <v>531245</v>
       </c>
       <c r="R6" t="n">
-        <v>6990455</v>
+        <v>6990446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,12 +1245,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,45 +1271,849 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Gammal sälg # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136293882</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136293891</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80564</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>531175</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293891</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136293892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80564</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>531175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6990373</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293892</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136293895</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80564</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>531191</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6990362</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293895</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>69300329</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>531232</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6990455</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Gammal sälg # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/69300329</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136293881</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57987</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531246</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6990446</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293881</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136293887</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57987</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>531225</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6990473</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293887</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136293888</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57987</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>531180</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6990438</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136293888</t>
         </is>
       </c>
     </row>
@@ -1310,6 +2124,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32502-2026 artfynd.xlsx
+++ b/artfynd/A 32502-2026 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>136293882</v>
       </c>
       <c r="B6" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136293891</v>
       </c>
       <c r="B7" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>136293892</v>
       </c>
       <c r="B8" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136293895</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136293881</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>136293887</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>136293888</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
